--- a/artfynd/A 1452-2026 artfynd.xlsx
+++ b/artfynd/A 1452-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112044167</v>
+        <v>97330373</v>
       </c>
       <c r="B2" t="n">
-        <v>56399</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100137</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555033</v>
+        <v>554999</v>
       </c>
       <c r="R2" t="n">
-        <v>6697976</v>
+        <v>6698264</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,19 +741,29 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -774,6 +780,1926 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>99589184</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Husby, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>555018</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6698279</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjolårsfru</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112044197</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>555034</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6698209</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96419223</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91282</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>554814</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6697751</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97121369</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>554998</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6698350</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97330695</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>554976</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6698330</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112044167</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100137</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slaguggla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Strix uralensis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>555033</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6697976</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>99589095</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Husby, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>554961</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6698257</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Uno Skog, Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99589220</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kyrkberget, Husby, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>555011</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6698313</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning under betad gammal tall.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96419312</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>554835</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6697664</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96801471</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>555013</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6698356</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-10-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-10-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96801489</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>555009</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6698357</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-10-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-10-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>97121049</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>555003</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6698356</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>97121063</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>555012</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6698358</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>97121134</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>555003</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6698365</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>97121317</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>555001</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6698364</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>97121323</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>554996</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6698355</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>97330496</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>554994</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6698363</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-11-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Intill gammal kolbotten</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1452-2026 artfynd.xlsx
+++ b/artfynd/A 1452-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96419223</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96419312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99589184</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112044197</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121369</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330695</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112044167</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99589095</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99589220</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96801471</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1996,6 +2056,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96801489</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2114,6 +2179,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121049</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2232,6 +2302,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121063</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2350,6 +2425,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121134</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2468,6 +2548,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121317</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2586,6 +2671,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97121323</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2700,8 +2790,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330496</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>